--- a/34th_Backgammon-championships_4c_output.xlsx
+++ b/34th_Backgammon-championships_4c_output.xlsx
@@ -1184,7 +1184,7 @@
         <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
         <v>7</v>
@@ -1257,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="n">
         <v>7</v>
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
         <v>8</v>
@@ -1602,7 +1602,7 @@
         <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N12" t="n">
         <v>9</v>
@@ -1620,7 +1620,7 @@
         <v>4</v>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
